--- a/exports/PNBHOUSING_full_report.xlsx
+++ b/exports/PNBHOUSING_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q67"/>
+  <dimension ref="A1:U67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,25 +557,25 @@
         <v>7.88</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44579.55208333334</v>
+        <v>44580.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>404.7</v>
+        <v>397.55</v>
       </c>
       <c r="I2" t="n">
         <v>400.0356025974033</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>0.06</v>
+        <v>-1.71</v>
       </c>
       <c r="L2" t="n">
         <v>2.2</v>
       </c>
       <c r="M2" t="n">
-        <v>0.04</v>
+        <v>0.21</v>
       </c>
       <c r="N2" t="n">
         <v>4.92</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>9.869999999999999</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44608.38541666666</v>
+        <v>44608.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>350.35</v>
+        <v>361.1</v>
       </c>
       <c r="I3" t="n">
         <v>356.736423942723</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>28</v>
+        <v>28.16666666666667</v>
       </c>
       <c r="K3" t="n">
-        <v>11.87</v>
+        <v>9.17</v>
       </c>
       <c r="L3" t="n">
         <v>2.8</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,25 +695,25 @@
         <v>9.880000000000001</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44615.55208333334</v>
+        <v>44616.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>332.9</v>
+        <v>317.4</v>
       </c>
       <c r="I4" t="n">
         <v>325.4149966063943</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>-7.81</v>
+        <v>-12.1</v>
       </c>
       <c r="L4" t="n">
-        <v>8.93</v>
+        <v>13.07</v>
       </c>
       <c r="M4" t="n">
-        <v>1.15</v>
+        <v>5.71</v>
       </c>
       <c r="N4" t="n">
         <v>7.23</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>13.89</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44652.55208333334</v>
+        <v>44655.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>323.9</v>
+        <v>338.95</v>
       </c>
       <c r="I5" t="n">
         <v>328.4226617691037</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.05</v>
+        <v>-6.79</v>
       </c>
       <c r="L5" t="n">
         <v>13.44</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>8.31</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44663.38541666666</v>
+        <v>44663.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>328.75</v>
+        <v>315.95</v>
       </c>
       <c r="I6" t="n">
         <v>324.067514756774</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.01</v>
+        <v>-6.79</v>
       </c>
       <c r="L6" t="n">
-        <v>3.63</v>
+        <v>7.39</v>
       </c>
       <c r="M6" t="n">
         <v>0.25</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>10.13</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44699.55208333334</v>
+        <v>44700.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>282.45</v>
+        <v>286.3</v>
       </c>
       <c r="I7" t="n">
         <v>284.3821659367177</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>36</v>
+        <v>36.83333333333334</v>
       </c>
       <c r="K7" t="n">
-        <v>10.6</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="L7" t="n">
         <v>11.77</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,25 +971,25 @@
         <v>10.9</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44722.55208333334</v>
+        <v>44725.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>304.55</v>
+        <v>292.8</v>
       </c>
       <c r="I8" t="n">
         <v>293.2211363963248</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K8" t="n">
-        <v>6.37</v>
+        <v>2.27</v>
       </c>
       <c r="L8" t="n">
         <v>8.59</v>
       </c>
       <c r="M8" t="n">
-        <v>1.99</v>
+        <v>2.51</v>
       </c>
       <c r="N8" t="n">
         <v>7.38</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>14.49</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44761.55208333334</v>
+        <v>44762.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>279.95</v>
+        <v>294.25</v>
       </c>
       <c r="I9" t="n">
         <v>287.1529097559107</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K9" t="n">
-        <v>4.39</v>
+        <v>-0.5</v>
       </c>
       <c r="L9" t="n">
-        <v>2.95</v>
+        <v>3.21</v>
       </c>
       <c r="M9" t="n">
         <v>2.62</v>
       </c>
       <c r="N9" t="n">
-        <v>2.12</v>
+        <v>5.07</v>
       </c>
       <c r="O9" t="n">
         <v>-4.19</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>6.7</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44802.38541666666</v>
+        <v>44802.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>289.7</v>
+        <v>287.65</v>
       </c>
       <c r="I10" t="n">
         <v>289.0492405438777</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>40</v>
+        <v>40.16666666666666</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.55</v>
+        <v>-2.24</v>
       </c>
       <c r="L10" t="n">
         <v>3.87</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>6.52</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44805.55208333334</v>
+        <v>44806.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>299.8</v>
+        <v>314.75</v>
       </c>
       <c r="I11" t="n">
         <v>306.2275580619559</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>3</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.22</v>
+        <v>-9.42</v>
       </c>
       <c r="L11" t="n">
-        <v>4.52</v>
+        <v>10.57</v>
       </c>
       <c r="M11" t="n">
         <v>0.66</v>
       </c>
       <c r="N11" t="n">
-        <v>3.72</v>
+        <v>4.7</v>
       </c>
       <c r="O11" t="n">
         <v>-2.41</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>8.710000000000001</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44827.55208333334</v>
+        <v>44830.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>334.75</v>
+        <v>323.3</v>
       </c>
       <c r="I12" t="n">
         <v>332.3808987400497</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K12" t="n">
-        <v>6.35</v>
+        <v>2.72</v>
       </c>
       <c r="L12" t="n">
         <v>4.65</v>
@@ -1125,7 +1268,7 @@
         <v>1.48</v>
       </c>
       <c r="N12" t="n">
-        <v>3.35</v>
+        <v>6.48</v>
       </c>
       <c r="O12" t="n">
         <v>4.7</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>11.45</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44853.38541666666</v>
+        <v>44853.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>340.8</v>
+        <v>352.9</v>
       </c>
       <c r="I13" t="n">
         <v>340.8976940235164</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.41</v>
+        <v>-9.16</v>
       </c>
       <c r="L13" t="n">
-        <v>7.72</v>
+        <v>9.77</v>
       </c>
       <c r="M13" t="n">
         <v>2.25</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>9.859999999999999</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44918.38541666666</v>
+        <v>44918.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>405.95</v>
+        <v>388.45</v>
       </c>
       <c r="I14" t="n">
         <v>392.3682594983627</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>64.83333333333333</v>
+        <v>65</v>
       </c>
       <c r="K14" t="n">
-        <v>15.03</v>
+        <v>10.07</v>
       </c>
       <c r="L14" t="n">
         <v>4.11</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>17.73</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44925.55208333334</v>
+        <v>44928.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>438.1</v>
+        <v>470.8</v>
       </c>
       <c r="I15" t="n">
         <v>457.3327151789307</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>7</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K15" t="n">
-        <v>-12.78</v>
+        <v>-21.2</v>
       </c>
       <c r="L15" t="n">
-        <v>15.16</v>
+        <v>21.93</v>
       </c>
       <c r="M15" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N15" t="n">
-        <v>4.75</v>
+        <v>8.33</v>
       </c>
       <c r="O15" t="n">
         <v>-7.49</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>15.56</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44946.55208333334</v>
+        <v>44949.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>444.05</v>
+        <v>440.9</v>
       </c>
       <c r="I16" t="n">
         <v>443.3401933973855</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K16" t="n">
-        <v>-5.68</v>
+        <v>-6.35</v>
       </c>
       <c r="L16" t="n">
-        <v>6.58</v>
+        <v>6.71</v>
       </c>
       <c r="M16" t="n">
         <v>0.29</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>8.82</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44965.38541666666</v>
+        <v>44965.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>472.85</v>
+        <v>486.75</v>
       </c>
       <c r="I17" t="n">
         <v>473.9751149433372</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K17" t="n">
-        <v>-7.25</v>
+        <v>-10.4</v>
       </c>
       <c r="L17" t="n">
-        <v>7.97</v>
+        <v>10.77</v>
       </c>
       <c r="M17" t="n">
         <v>6.63</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>10.55</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44998.55208333334</v>
+        <v>44999.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>484.5</v>
+        <v>450.7</v>
       </c>
       <c r="I18" t="n">
         <v>483.3910520870083</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>33</v>
+        <v>33.83333333333334</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.46</v>
+        <v>-7.41</v>
       </c>
       <c r="L18" t="n">
-        <v>4.52</v>
+        <v>8</v>
       </c>
       <c r="M18" t="n">
         <v>1.32</v>
       </c>
       <c r="N18" t="n">
-        <v>4.23</v>
+        <v>9.23</v>
       </c>
       <c r="O18" t="n">
         <v>5.32</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>15.29</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45014.55208333334</v>
+        <v>45016.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>403.2</v>
+        <v>438.5</v>
       </c>
       <c r="I19" t="n">
         <v>427.4872392346723</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K19" t="n">
-        <v>10.54</v>
+        <v>2.71</v>
       </c>
       <c r="L19" t="n">
         <v>8.73</v>
       </c>
       <c r="M19" t="n">
-        <v>1.29</v>
+        <v>1.69</v>
       </c>
       <c r="N19" t="n">
-        <v>3.85</v>
+        <v>5.27</v>
       </c>
       <c r="O19" t="n">
         <v>-9.23</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>14.57</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45107.38541666666</v>
+        <v>45107.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>574.8</v>
+        <v>566.2</v>
       </c>
       <c r="I20" t="n">
         <v>571.809225962642</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>91</v>
+        <v>91.16666666666667</v>
       </c>
       <c r="K20" t="n">
-        <v>31.08</v>
+        <v>29.12</v>
       </c>
       <c r="L20" t="n">
         <v>7.26</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>121</v>
+        <v>122</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>8.050000000000001</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45114.55208333334</v>
+        <v>45117.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>583.05</v>
+        <v>604.15</v>
       </c>
       <c r="I21" t="n">
         <v>601.3335454959712</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>7</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.98</v>
+        <v>-6.7</v>
       </c>
       <c r="L21" t="n">
-        <v>4.24</v>
+        <v>7.12</v>
       </c>
       <c r="M21" t="n">
         <v>0.66</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>8.640000000000001</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45134.38541666666</v>
+        <v>45134.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>654</v>
+        <v>641</v>
       </c>
       <c r="I22" t="n">
         <v>643.6236404430083</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K22" t="n">
-        <v>8.25</v>
+        <v>6.1</v>
       </c>
       <c r="L22" t="n">
         <v>4.35</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>8.09</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45149.38541666666</v>
+        <v>45149.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>657.55</v>
+        <v>658.3</v>
       </c>
       <c r="I23" t="n">
         <v>658.1129932341084</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>14.83333333333333</v>
+        <v>15</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.58</v>
+        <v>-2.7</v>
       </c>
       <c r="L23" t="n">
-        <v>3.35</v>
+        <v>3.57</v>
       </c>
       <c r="M23" t="n">
         <v>0.45</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>6.53</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45194.38541666666</v>
+        <v>45194.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>668.45</v>
+        <v>659</v>
       </c>
       <c r="I24" t="n">
         <v>663.4068791157521</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>44.83333333333334</v>
+        <v>45</v>
       </c>
       <c r="K24" t="n">
-        <v>1.54</v>
+        <v>0.11</v>
       </c>
       <c r="L24" t="n">
         <v>4.9</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>9.970000000000001</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45198.55208333334</v>
+        <v>45202.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>690.5</v>
+        <v>744.3</v>
       </c>
       <c r="I25" t="n">
         <v>712.2984358001188</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>4</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.78</v>
+        <v>-12.94</v>
       </c>
       <c r="L25" t="n">
-        <v>5.9</v>
+        <v>13.02</v>
       </c>
       <c r="M25" t="n">
         <v>0.92</v>
       </c>
       <c r="N25" t="n">
-        <v>2.77</v>
+        <v>7.31</v>
       </c>
       <c r="O25" t="n">
         <v>-4.77</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>12.29</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45222.38541666666</v>
+        <v>45222.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>746.85</v>
+        <v>704.2</v>
       </c>
       <c r="I26" t="n">
         <v>714.8785174800497</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K26" t="n">
-        <v>0.34</v>
+        <v>-5.39</v>
       </c>
       <c r="L26" t="n">
         <v>7.44</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>13.02</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45243.38541666666</v>
+        <v>45243.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>767.4</v>
+        <v>775</v>
       </c>
       <c r="I27" t="n">
         <v>774.9879778226964</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>20.83333333333333</v>
+        <v>21</v>
       </c>
       <c r="K27" t="n">
-        <v>-8.970000000000001</v>
+        <v>-10.05</v>
       </c>
       <c r="L27" t="n">
-        <v>9.210000000000001</v>
+        <v>10.66</v>
       </c>
       <c r="M27" t="n">
         <v>3.1</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>6.63</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45320.38541666666</v>
+        <v>45320.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>799.9</v>
+        <v>789.9</v>
       </c>
       <c r="I28" t="n">
         <v>797.657902920031</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>76.83333333333333</v>
+        <v>77</v>
       </c>
       <c r="K28" t="n">
-        <v>3.21</v>
+        <v>1.92</v>
       </c>
       <c r="L28" t="n">
         <v>15.99</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>14.47</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45379.55208333334</v>
+        <v>45383.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>627.65</v>
+        <v>713.85</v>
       </c>
       <c r="I29" t="n">
         <v>678.7787347608619</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>59</v>
+        <v>62.83333333333334</v>
       </c>
       <c r="K29" t="n">
-        <v>20.54</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="L29" t="n">
         <v>7.05</v>
       </c>
       <c r="M29" t="n">
-        <v>3.45</v>
+        <v>3.72</v>
       </c>
       <c r="N29" t="n">
-        <v>5.54</v>
+        <v>20.42</v>
       </c>
       <c r="O29" t="n">
         <v>-3.83</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>13.89</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45421.55208333334</v>
+        <v>45422.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>752.65</v>
+        <v>742.6</v>
       </c>
       <c r="I30" t="n">
         <v>742.6075140632188</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K30" t="n">
-        <v>5.44</v>
+        <v>4.03</v>
       </c>
       <c r="L30" t="n">
         <v>8.800000000000001</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>7.3</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45434.55208333334</v>
+        <v>45435.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>744.5</v>
+        <v>802.5</v>
       </c>
       <c r="I31" t="n">
         <v>777.1073504813834</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.26</v>
+        <v>-8.07</v>
       </c>
       <c r="L31" t="n">
-        <v>1.97</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="M31" t="n">
-        <v>0.62</v>
+        <v>0.82</v>
       </c>
       <c r="N31" t="n">
-        <v>1.71</v>
+        <v>7.32</v>
       </c>
       <c r="O31" t="n">
         <v>-1.85</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>9.380000000000001</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45440.55208333334</v>
+        <v>45441.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>788</v>
+        <v>745.8</v>
       </c>
       <c r="I32" t="n">
         <v>751.8008106210031</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.81</v>
+        <v>-7.07</v>
       </c>
       <c r="L32" t="n">
-        <v>6.47</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>0.01</v>
+        <v>5.58</v>
       </c>
       <c r="N32" t="n">
-        <v>1.75</v>
+        <v>6.73</v>
       </c>
       <c r="O32" t="n">
         <v>7.32</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>7.12</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45450.55208333334</v>
+        <v>45453.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>751</v>
+        <v>761.6</v>
       </c>
       <c r="I33" t="n">
         <v>761.5886854766912</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.7</v>
+        <v>-2.12</v>
       </c>
       <c r="L33" t="n">
-        <v>0.9399999999999999</v>
+        <v>3.78</v>
       </c>
       <c r="M33" t="n">
         <v>4.15</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>10</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45464.38541666666</v>
+        <v>45464.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>794.95</v>
+        <v>782.55</v>
       </c>
       <c r="I34" t="n">
         <v>790.1615072026445</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K34" t="n">
-        <v>4.38</v>
+        <v>2.75</v>
       </c>
       <c r="L34" t="n">
         <v>1.33</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>11.26</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45504.55208333334</v>
+        <v>45505.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>806.05</v>
+        <v>820.6</v>
       </c>
       <c r="I35" t="n">
         <v>816.2033882009532</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>40</v>
+        <v>40.83333333333334</v>
       </c>
       <c r="K35" t="n">
-        <v>-3</v>
+        <v>-4.86</v>
       </c>
       <c r="L35" t="n">
-        <v>5.11</v>
+        <v>5.55</v>
       </c>
       <c r="M35" t="n">
         <v>1.79</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>6.96</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45558.55208333334</v>
+        <v>45559.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>1013</v>
+        <v>1005.7</v>
       </c>
       <c r="I36" t="n">
         <v>1009.19961974286</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>53.16666666666666</v>
+        <v>54</v>
       </c>
       <c r="K36" t="n">
-        <v>23.45</v>
+        <v>22.56</v>
       </c>
       <c r="L36" t="n">
         <v>6.4</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>11.92</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45587.55208333334</v>
+        <v>45588.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>879</v>
+        <v>953.25</v>
       </c>
       <c r="I37" t="n">
         <v>952.9194674064344</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K37" t="n">
-        <v>12.6</v>
+        <v>5.22</v>
       </c>
       <c r="L37" t="n">
         <v>2.22</v>
@@ -2550,7 +2993,7 @@
         <v>1.4</v>
       </c>
       <c r="N37" t="n">
-        <v>2.6</v>
+        <v>6.55</v>
       </c>
       <c r="O37" t="n">
         <v>-1.73</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>13.58</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45610.38541666666</v>
+        <v>45610.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>939.05</v>
+        <v>897.35</v>
       </c>
       <c r="I38" t="n">
         <v>914.7247246093702</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K38" t="n">
-        <v>-1.49</v>
+        <v>-5.86</v>
       </c>
       <c r="L38" t="n">
         <v>7.94</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>13.73</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45630.55208333334</v>
+        <v>45631.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>914</v>
+        <v>940.3</v>
       </c>
       <c r="I39" t="n">
         <v>936.2501343091784</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K39" t="n">
-        <v>-1.86</v>
+        <v>-4.79</v>
       </c>
       <c r="L39" t="n">
-        <v>4.81</v>
+        <v>5.2</v>
       </c>
       <c r="M39" t="n">
         <v>2</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>7.98</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45642.55208333334</v>
+        <v>45643.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>920.55</v>
+        <v>898.1</v>
       </c>
       <c r="I40" t="n">
         <v>904.0109350646765</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K40" t="n">
-        <v>-2.1</v>
+        <v>-4.49</v>
       </c>
       <c r="L40" t="n">
-        <v>2.87</v>
+        <v>4.57</v>
       </c>
       <c r="M40" t="n">
         <v>0.22</v>
       </c>
       <c r="N40" t="n">
-        <v>2.27</v>
+        <v>3.48</v>
       </c>
       <c r="O40" t="n">
         <v>3.17</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>7.43</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45658.55208333334</v>
+        <v>45659.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>903.5</v>
+        <v>927.9</v>
       </c>
       <c r="I41" t="n">
         <v>904.9111452818526</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.6</v>
+        <v>-3.32</v>
       </c>
       <c r="L41" t="n">
-        <v>2.62</v>
+        <v>3.98</v>
       </c>
       <c r="M41" t="n">
         <v>2.13</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>9.57</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45666.55208333334</v>
+        <v>45667.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>887.5</v>
+        <v>855.5</v>
       </c>
       <c r="I42" t="n">
         <v>863.7476377434348</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K42" t="n">
-        <v>-4.35</v>
+        <v>-7.8</v>
       </c>
       <c r="L42" t="n">
-        <v>7.32</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="M42" t="n">
         <v>0.97</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>10.17</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45672.55208333334</v>
+        <v>45673.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>851.1</v>
+        <v>886.4</v>
       </c>
       <c r="I43" t="n">
         <v>881.4352528671812</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K43" t="n">
-        <v>0.51</v>
+        <v>-3.61</v>
       </c>
       <c r="L43" t="n">
         <v>4.3</v>
@@ -2892,7 +3407,7 @@
         <v>1.54</v>
       </c>
       <c r="N43" t="n">
-        <v>4.13</v>
+        <v>5.09</v>
       </c>
       <c r="O43" t="n">
         <v>-3.9</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>10.14</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45681.55208333334</v>
+        <v>45684.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>864</v>
+        <v>816.5</v>
       </c>
       <c r="I44" t="n">
         <v>844.8864808490574</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K44" t="n">
-        <v>-2.53</v>
+        <v>-7.89</v>
       </c>
       <c r="L44" t="n">
-        <v>4.46</v>
+        <v>12.43</v>
       </c>
       <c r="M44" t="n">
-        <v>0.11</v>
+        <v>0.46</v>
       </c>
       <c r="N44" t="n">
-        <v>2.6</v>
+        <v>6.01</v>
       </c>
       <c r="O44" t="n">
         <v>5.09</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>12.49</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45692.55208333334</v>
+        <v>45693.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>871</v>
+        <v>906.05</v>
       </c>
       <c r="I45" t="n">
         <v>904.8514889513941</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K45" t="n">
-        <v>-6.67</v>
+        <v>-10.97</v>
       </c>
       <c r="L45" t="n">
         <v>12.89</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>11.11</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45698.55208333334</v>
+        <v>45699.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>863</v>
+        <v>830</v>
       </c>
       <c r="I46" t="n">
         <v>841.1284814916511</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K46" t="n">
-        <v>-4.75</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>5.3</v>
+        <v>8.56</v>
       </c>
       <c r="M46" t="n">
-        <v>0.02</v>
+        <v>1.1</v>
       </c>
       <c r="N46" t="n">
-        <v>2.91</v>
+        <v>3.77</v>
       </c>
       <c r="O46" t="n">
         <v>3.21</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>11</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45735.38541666666</v>
+        <v>45735.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>822</v>
+        <v>834</v>
       </c>
       <c r="I47" t="n">
         <v>823.6484363852492</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>36</v>
+        <v>36.16666666666666</v>
       </c>
       <c r="K47" t="n">
-        <v>0.96</v>
+        <v>-0.48</v>
       </c>
       <c r="L47" t="n">
         <v>4.09</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>7.46</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45820.55208333334</v>
+        <v>45821.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>1086</v>
+        <v>1054.8</v>
       </c>
       <c r="I48" t="n">
         <v>1067.511592395156</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>85</v>
+        <v>85.83333333333333</v>
       </c>
       <c r="K48" t="n">
-        <v>30.22</v>
+        <v>26.47</v>
       </c>
       <c r="L48" t="n">
         <v>1.65</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>111</v>
+        <v>112</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>4</v>
+      </c>
+      <c r="U48" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>6.66</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45833.55208333334</v>
+        <v>45834.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>1087.1</v>
+        <v>1095.9</v>
       </c>
       <c r="I49" t="n">
         <v>1092.569298986863</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K49" t="n">
-        <v>-3.06</v>
+        <v>-3.9</v>
       </c>
       <c r="L49" t="n">
-        <v>4</v>
+        <v>4.83</v>
       </c>
       <c r="M49" t="n">
         <v>1.4</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>5.8</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45860.55208333334</v>
+        <v>45861.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>1082.6</v>
+        <v>1057</v>
       </c>
       <c r="I50" t="n">
         <v>1057.488387419917</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K50" t="n">
-        <v>-1.21</v>
+        <v>-3.55</v>
       </c>
       <c r="L50" t="n">
-        <v>3.55</v>
+        <v>5.56</v>
       </c>
       <c r="M50" t="n">
         <v>0.1</v>
       </c>
       <c r="N50" t="n">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="O50" t="n">
         <v>1.94</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>7.06</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45887.55208333334</v>
+        <v>45888.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>786.5</v>
+        <v>817.8</v>
       </c>
       <c r="I51" t="n">
         <v>813.9900636078282</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K51" t="n">
-        <v>25.59</v>
+        <v>22.63</v>
       </c>
       <c r="L51" t="n">
         <v>2.74</v>
@@ -3348,7 +3959,7 @@
         <v>1.3</v>
       </c>
       <c r="N51" t="n">
-        <v>2.54</v>
+        <v>4.09</v>
       </c>
       <c r="O51" t="n">
         <v>-1.82</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>7.92</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45897.38541666666</v>
+        <v>45897.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>772.6</v>
+        <v>769</v>
       </c>
       <c r="I52" t="n">
         <v>772.548264266904</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K52" t="n">
-        <v>-5.53</v>
+        <v>-5.97</v>
       </c>
       <c r="L52" t="n">
-        <v>5.94</v>
+        <v>6.43</v>
       </c>
       <c r="M52" t="n">
         <v>0.12</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>5.1</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45905.55208333334</v>
+        <v>45908.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>792.5</v>
+        <v>804.95</v>
       </c>
       <c r="I53" t="n">
         <v>794.87627843966</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>8</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K53" t="n">
-        <v>-3.06</v>
+        <v>-4.67</v>
       </c>
       <c r="L53" t="n">
-        <v>3.71</v>
+        <v>5.59</v>
       </c>
       <c r="M53" t="n">
         <v>1.28</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>5.2</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45940.38541666666</v>
+        <v>45940.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>860.95</v>
+        <v>855.35</v>
       </c>
       <c r="I54" t="n">
         <v>858.5635391297083</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>32</v>
+        <v>32.16666666666666</v>
       </c>
       <c r="K54" t="n">
-        <v>6.96</v>
+        <v>6.26</v>
       </c>
       <c r="L54" t="n">
         <v>1.5</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,25 +4214,25 @@
         <v>5.45</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45951.57291666666</v>
+        <v>45953.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>873</v>
+        <v>886.05</v>
       </c>
       <c r="I55" t="n">
         <v>877.4613679473429</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>11.02083333333333</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K55" t="n">
-        <v>-2.06</v>
+        <v>-3.59</v>
       </c>
       <c r="L55" t="n">
-        <v>2.76</v>
+        <v>4.28</v>
       </c>
       <c r="M55" t="n">
-        <v>0.49</v>
+        <v>0.76</v>
       </c>
       <c r="N55" t="n">
         <v>3.77</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>5.57</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45971.55208333334</v>
+        <v>45972.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>900.2</v>
+        <v>893</v>
       </c>
       <c r="I56" t="n">
         <v>893.3477749978164</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K56" t="n">
-        <v>1.6</v>
+        <v>0.78</v>
       </c>
       <c r="L56" t="n">
         <v>1.7</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>5.2</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45987.38541666666</v>
+        <v>45987.55208333334</v>
       </c>
       <c r="H57" t="n">
-        <v>913.95</v>
+        <v>916.4</v>
       </c>
       <c r="I57" t="n">
         <v>914.5284243624044</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K57" t="n">
-        <v>-2.35</v>
+        <v>-2.62</v>
       </c>
       <c r="L57" t="n">
         <v>5.59</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>4.96</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46041.38541666666</v>
+        <v>46041.55208333334</v>
       </c>
       <c r="H58" t="n">
-        <v>959.8</v>
+        <v>955.55</v>
       </c>
       <c r="I58" t="n">
         <v>957.4845300303158</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>53.83333333333334</v>
+        <v>54</v>
       </c>
       <c r="K58" t="n">
-        <v>4.74</v>
+        <v>4.27</v>
       </c>
       <c r="L58" t="n">
         <v>6.72</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>5.59</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46118.38541666666</v>
+        <v>46118.55208333334</v>
       </c>
       <c r="H59" t="n">
-        <v>805.35</v>
+        <v>819</v>
       </c>
       <c r="I59" t="n">
         <v>814.1566302060269</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>76.83333333333333</v>
+        <v>77</v>
       </c>
       <c r="K59" t="n">
-        <v>15.72</v>
+        <v>14.29</v>
       </c>
       <c r="L59" t="n">
         <v>1.19</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>4</v>
+      </c>
+      <c r="U59" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>9.1</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46171.55208333334</v>
+        <v>46174.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>1045</v>
+        <v>1013.4</v>
       </c>
       <c r="I60" t="n">
         <v>1038.881163154596</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>53</v>
+        <v>55.83333333333334</v>
       </c>
       <c r="K60" t="n">
-        <v>27.59</v>
+        <v>23.74</v>
       </c>
       <c r="L60" t="n">
         <v>1.81</v>
@@ -3861,7 +4580,7 @@
         <v>1.39</v>
       </c>
       <c r="N60" t="n">
-        <v>2.75</v>
+        <v>4.2</v>
       </c>
       <c r="O60" t="n">
         <v>5.05</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>8.19</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46188.38541666666</v>
+        <v>46188.55208333334</v>
       </c>
       <c r="H61" t="n">
-        <v>1014</v>
+        <v>1018</v>
       </c>
       <c r="I61" t="n">
         <v>1016.156861933064</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.06</v>
+        <v>-0.45</v>
       </c>
       <c r="L61" t="n">
         <v>3.5</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>6.22</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46232.55208333334</v>
+        <v>46233.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>1059</v>
+        <v>1032.5</v>
       </c>
       <c r="I62" t="n">
         <v>1048.89097788143</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>44</v>
+        <v>44.83333333333334</v>
       </c>
       <c r="K62" t="n">
-        <v>4.03</v>
+        <v>1.42</v>
       </c>
       <c r="L62" t="n">
         <v>2.78</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>7.21</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46238.55208333334</v>
+        <v>46239.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>1080.4</v>
+        <v>1134.6</v>
       </c>
       <c r="I63" t="n">
         <v>1093.129740597958</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K63" t="n">
-        <v>-4.64</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="L63" t="n">
-        <v>6</v>
+        <v>11.77</v>
       </c>
       <c r="M63" t="n">
         <v>0.48</v>
       </c>
       <c r="N63" t="n">
-        <v>3.62</v>
+        <v>3.67</v>
       </c>
       <c r="O63" t="n">
         <v>-2.62</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>9.720000000000001</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46267.38541666666</v>
+        <v>46267.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>1140.6</v>
+        <v>1134</v>
       </c>
       <c r="I64" t="n">
         <v>1140.406138623571</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>28</v>
+        <v>28.16666666666667</v>
       </c>
       <c r="K64" t="n">
-        <v>0.53</v>
+        <v>-0.05</v>
       </c>
       <c r="L64" t="n">
         <v>5.68</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>4.99</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46302.55208333334</v>
+        <v>46303.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>1136</v>
+        <v>1160.9</v>
       </c>
       <c r="I65" t="n">
         <v>1150.987034611514</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>35</v>
+        <v>35.83333333333334</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.18</v>
+        <v>-2.37</v>
       </c>
       <c r="L65" t="n">
         <v>5.38</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>7.1</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46316.38541666666</v>
+        <v>46316.55208333334</v>
       </c>
       <c r="H66" t="n">
-        <v>1146.6</v>
+        <v>1141.1</v>
       </c>
       <c r="I66" t="n">
         <v>1145.181674304388</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K66" t="n">
-        <v>-1.23</v>
+        <v>-1.71</v>
       </c>
       <c r="L66" t="n">
         <v>2.56</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4263,6 +5066,12 @@
       <c r="Q67" t="n">
         <v>9</v>
       </c>
+      <c r="R67" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6365,7 +7174,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.8</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="6">
@@ -6375,7 +7184,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="7">
@@ -6385,7 +7194,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>91</v>
+        <v>91.2</v>
       </c>
     </row>
     <row r="8">
@@ -6395,7 +7204,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="9">
@@ -6405,7 +7214,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="10">
@@ -6415,7 +7224,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>53.6</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="11">
@@ -6455,7 +7264,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.64</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="15">
@@ -6465,7 +7274,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.17</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="16">
@@ -6475,7 +7284,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.06</v>
+        <v>-2.58</v>
       </c>
     </row>
     <row r="17">
@@ -6485,7 +7294,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31.08</v>
+        <v>29.12</v>
       </c>
     </row>
     <row r="18">
@@ -6495,7 +7304,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>44.6</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="19">
@@ -6505,7 +7314,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.39</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="20">
@@ -6515,7 +7324,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.52</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="21">
@@ -6525,7 +7334,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15.99</v>
+        <v>21.93</v>
       </c>
     </row>
     <row r="22">
@@ -6535,7 +7344,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23">
@@ -6545,7 +7354,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
@@ -6555,7 +7364,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="25">
@@ -6575,7 +7384,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.15</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="27">
@@ -6585,7 +7394,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10.09</v>
+        <v>20.42</v>
       </c>
     </row>
     <row r="28">
@@ -6595,7 +7404,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29">
